--- a/data/trans_camb/P19C03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 4,46</t>
+          <t>-9,92; 4,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -0,2</t>
+          <t>-14,13; 0,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,64; -4,26</t>
+          <t>-23,24; -4,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 3,09</t>
+          <t>-10,7; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -1,56</t>
+          <t>-14,73; -1,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,12; -7,97</t>
+          <t>-24,74; -7,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 1,84</t>
+          <t>-7,84; 1,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -2,91</t>
+          <t>-12,25; -3,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,13; -8,59</t>
+          <t>-21,08; -8,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 13,8</t>
+          <t>-24,24; 13,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 0,38</t>
+          <t>-36,12; 1,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,32; -11,9</t>
+          <t>-61,9; -15,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 10,2</t>
+          <t>-28,71; 10,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,0; -4,74</t>
+          <t>-40,18; -4,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,13; -25,1</t>
+          <t>-67,33; -23,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 5,61</t>
+          <t>-21,21; 4,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,16; -9,07</t>
+          <t>-33,18; -10,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,89; -25,37</t>
+          <t>-59,29; -27,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 0,54</t>
+          <t>-11,39; 0,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 0,46</t>
+          <t>-12,41; 0,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,99; -9,74</t>
+          <t>-23,6; -9,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 0,69</t>
+          <t>-11,49; 0,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,54; -3,15</t>
+          <t>-15,07; -3,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,05; -15,98</t>
+          <t>-30,14; -16,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -1,44</t>
+          <t>-9,51; -1,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,71; -2,97</t>
+          <t>-11,53; -3,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -15,32</t>
+          <t>-25,19; -14,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 1,39</t>
+          <t>-27,16; 0,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 0,86</t>
+          <t>-29,0; 0,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,16; -25,04</t>
+          <t>-56,2; -25,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 1,37</t>
+          <t>-27,23; 1,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,8; -8,46</t>
+          <t>-35,56; -9,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,6; -44,19</t>
+          <t>-73,06; -43,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,74; -3,58</t>
+          <t>-22,88; -3,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -7,62</t>
+          <t>-27,76; -8,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,62; -40,3</t>
+          <t>-62,07; -39,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,56</t>
+          <t>-10,74; 1,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 1,13</t>
+          <t>-11,11; 0,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -10,7</t>
+          <t>-21,85; -9,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,26</t>
+          <t>-6,96; 4,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -1,93</t>
+          <t>-11,96; -1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -11,35</t>
+          <t>-20,73; -10,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,8</t>
+          <t>-7,29; 0,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -2,13</t>
+          <t>-10,11; -1,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,72; -12,13</t>
+          <t>-19,77; -12,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 4,44</t>
+          <t>-25,79; 3,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 3,15</t>
+          <t>-26,54; 2,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,38; -29,24</t>
+          <t>-52,57; -26,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 12,66</t>
+          <t>-17,03; 12,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -5,22</t>
+          <t>-30,46; -3,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,25; -32,99</t>
+          <t>-51,59; -31,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 2,14</t>
+          <t>-18,25; 2,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,98; -6,05</t>
+          <t>-25,23; -5,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,43; -33,97</t>
+          <t>-49,78; -34,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 4,48</t>
+          <t>-8,91; 3,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -1,35</t>
+          <t>-14,59; -1,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,47; -11,38</t>
+          <t>-31,49; -11,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 1,52</t>
+          <t>-11,17; 1,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,12; -0,29</t>
+          <t>-12,63; -0,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 2,67</t>
+          <t>-17,23; 0,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,17</t>
+          <t>-8,05; 1,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -2,96</t>
+          <t>-11,04; -2,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -9,72</t>
+          <t>-23,77; -8,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 14,58</t>
+          <t>-22,9; 11,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,17; -4,3</t>
+          <t>-36,96; -3,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,17; -33,32</t>
+          <t>-80,69; -33,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 4,8</t>
+          <t>-28,61; 5,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,05; -0,98</t>
+          <t>-33,11; -0,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 11,01</t>
+          <t>-45,78; 2,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 3,39</t>
+          <t>-21,73; 3,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,7; -8,05</t>
+          <t>-29,27; -7,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -28,43</t>
+          <t>-66,56; -27,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,96</t>
+          <t>3,0; 16,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 6,69</t>
+          <t>-6,3; 6,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,34</t>
+          <t>-6,97; 4,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 9,0</t>
+          <t>-5,86; 8,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 0,91</t>
+          <t>-13,12; 0,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -4,12</t>
+          <t>-15,1; -3,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 10,4</t>
+          <t>0,02; 10,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 1,34</t>
+          <t>-7,93; 1,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -1,78</t>
+          <t>-9,44; -1,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13,9; 103,46</t>
+          <t>11,42; 100,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 40,67</t>
+          <t>-26,71; 37,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 32,41</t>
+          <t>-28,73; 24,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 33,61</t>
+          <t>-17,19; 32,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 4,39</t>
+          <t>-38,85; 3,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,78; -16,03</t>
+          <t>-42,56; -14,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,64; 45,45</t>
+          <t>0,1; 44,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 5,94</t>
+          <t>-28,52; 6,97</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,72; -7,69</t>
+          <t>-32,88; -6,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 9,3</t>
+          <t>-2,68; 10,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 13,16</t>
+          <t>-0,3; 13,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,88</t>
+          <t>-4,62; 5,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 4,92</t>
+          <t>-7,26; 6,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 7,94</t>
+          <t>-6,33; 7,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -3,04</t>
+          <t>-21,37; -3,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 6,46</t>
+          <t>-3,48; 6,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 8,63</t>
+          <t>-0,87; 8,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -0,49</t>
+          <t>-12,22; -0,65</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 98,42</t>
+          <t>-19,78; 118,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 142,93</t>
+          <t>-2,22; 151,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 69,85</t>
+          <t>-29,9; 65,55</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 30,44</t>
+          <t>-29,56; 36,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 46,57</t>
+          <t>-24,95; 46,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-81,75; -15,78</t>
+          <t>-82,65; -15,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 45,35</t>
+          <t>-17,53; 44,71</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 61,49</t>
+          <t>-4,79; 57,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,98; -4,0</t>
+          <t>-65,47; -4,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 8,39</t>
+          <t>-4,49; 7,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,32</t>
+          <t>-2,09; 10,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 6,86</t>
+          <t>-3,78; 6,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 5,65</t>
+          <t>-3,25; 5,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,6; 13,14</t>
+          <t>1,21; 14,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,81</t>
+          <t>-1,78; 5,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,34</t>
+          <t>-1,87; 5,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,39; 10,21</t>
+          <t>1,57; 10,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,18</t>
+          <t>-0,95; 4,95</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 365,47</t>
+          <t>-53,19; 299,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 386,32</t>
+          <t>-32,01; 416,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 286,74</t>
+          <t>-37,38; 264,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 184,67</t>
+          <t>-40,67; 219,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 383,34</t>
+          <t>2,91; 388,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 210,44</t>
+          <t>-22,43; 182,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 146,62</t>
+          <t>-26,82; 144,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>12,32; 258,59</t>
+          <t>20,63; 282,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 162,3</t>
+          <t>-12,57; 141,75</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,59</t>
+          <t>-4,59; 0,43</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,73</t>
+          <t>-6,92; -1,84</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,39; -11,29</t>
+          <t>-18,41; -11,35</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,84</t>
+          <t>-5,43; -0,57</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -3,15</t>
+          <t>-8,11; -3,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-18,2; -11,53</t>
+          <t>-18,25; -11,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,76</t>
+          <t>-4,53; -0,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -3,45</t>
+          <t>-6,89; -3,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -12,26</t>
+          <t>-16,68; -12,24</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 1,98</t>
+          <t>-13,73; 1,46</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -5,98</t>
+          <t>-20,69; -5,48</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-56,54; -36,05</t>
+          <t>-57,45; -36,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -2,93</t>
+          <t>-16,3; -1,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -10,36</t>
+          <t>-24,45; -10,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-55,51; -36,97</t>
+          <t>-55,08; -37,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,36</t>
+          <t>-13,74; -3,14</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -11,16</t>
+          <t>-20,87; -10,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -38,94</t>
+          <t>-51,4; -39,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-14,84</t>
+          <t>-13,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,6</t>
+          <t>-16,77</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,4</t>
+          <t>-14,89</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 4,33</t>
+          <t>-9,96; 3,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 0,68</t>
+          <t>-14,4; 0,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,24; -4,97</t>
+          <t>-22,45; -4,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 2,95</t>
+          <t>-11,19; 2,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -1,26</t>
+          <t>-14,64; -1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -7,74</t>
+          <t>-23,87; -9,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 1,68</t>
+          <t>-7,57; 1,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -3,32</t>
+          <t>-12,32; -2,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -8,79</t>
+          <t>-21,01; -8,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-41,01%</t>
+          <t>-37,04%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-50,14%</t>
+          <t>-50,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-44,5%</t>
+          <t>-43,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 13,66</t>
+          <t>-25,58; 12,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 1,93</t>
+          <t>-36,54; -0,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -15,55</t>
+          <t>-57,41; -12,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 10,05</t>
+          <t>-30,11; 8,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -4,11</t>
+          <t>-40,07; -5,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -23,53</t>
+          <t>-67,06; -28,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 4,96</t>
+          <t>-20,58; 5,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,18; -10,14</t>
+          <t>-33,48; -8,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,29; -27,11</t>
+          <t>-57,49; -26,41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-16,85</t>
+          <t>-17,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-22,41</t>
+          <t>-19,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-19,95</t>
+          <t>-18,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 0,21</t>
+          <t>-11,02; -0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 0,05</t>
+          <t>-11,84; -0,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,6; -9,38</t>
+          <t>-24,42; -11,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 0,42</t>
+          <t>-11,12; 0,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -3,58</t>
+          <t>-14,75; -3,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,14; -16,37</t>
+          <t>-25,05; -13,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -1,37</t>
+          <t>-9,88; -1,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -3,24</t>
+          <t>-11,71; -3,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,19; -14,9</t>
+          <t>-22,83; -14,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-42,34%</t>
+          <t>-44,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-56,86%</t>
+          <t>-49,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-50,38%</t>
+          <t>-46,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 0,53</t>
+          <t>-26,12; -0,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 0,11</t>
+          <t>-28,4; -0,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,2; -25,18</t>
+          <t>-57,22; -29,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 1,19</t>
+          <t>-26,15; 2,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,56; -9,42</t>
+          <t>-35,5; -9,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,06; -43,88</t>
+          <t>-59,64; -36,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,88; -3,42</t>
+          <t>-23,54; -4,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,76; -8,78</t>
+          <t>-28,21; -9,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -39,57</t>
+          <t>-54,65; -37,73</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-16,14</t>
+          <t>-17,18</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-16,02</t>
+          <t>-15,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-16,02</t>
+          <t>-16,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 1,33</t>
+          <t>-10,45; 0,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 0,79</t>
+          <t>-10,95; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -9,28</t>
+          <t>-22,83; -11,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 4,49</t>
+          <t>-6,94; 4,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -1,33</t>
+          <t>-12,6; -1,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,73; -10,88</t>
+          <t>-20,02; -10,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,95</t>
+          <t>-7,09; 1,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -1,96</t>
+          <t>-10,16; -1,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,77; -12,15</t>
+          <t>-20,03; -12,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-41,81%</t>
+          <t>-44,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,1%</t>
+          <t>-41,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,36%</t>
+          <t>-42,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 3,68</t>
+          <t>-24,87; 0,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 2,13</t>
+          <t>-26,05; 1,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,57; -26,55</t>
+          <t>-54,31; -31,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 12,89</t>
+          <t>-17,71; 12,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,46; -3,98</t>
+          <t>-31,05; -3,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,59; -31,86</t>
+          <t>-50,47; -29,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 2,56</t>
+          <t>-17,76; 2,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,23; -5,65</t>
+          <t>-25,38; -4,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,78; -34,27</t>
+          <t>-50,1; -34,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-19,66</t>
+          <t>-13,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,95</t>
+          <t>-14,21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-15,75</t>
+          <t>-13,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 3,5</t>
+          <t>-8,78; 4,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -1,37</t>
+          <t>-13,82; -1,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -11,29</t>
+          <t>-19,43; -7,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 1,63</t>
+          <t>-10,68; 1,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -0,24</t>
+          <t>-12,38; -0,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 0,26</t>
+          <t>-19,55; -9,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,07</t>
+          <t>-7,96; 1,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -2,63</t>
+          <t>-11,7; -2,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,77; -8,98</t>
+          <t>-17,63; -9,77</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-55,68%</t>
+          <t>-37,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,17%</t>
+          <t>-40,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-44,7%</t>
+          <t>-39,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 11,43</t>
+          <t>-22,42; 13,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,96; -3,22</t>
+          <t>-35,66; -4,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,69; -33,88</t>
+          <t>-49,33; -22,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 5,37</t>
+          <t>-28,09; 3,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,11; -0,94</t>
+          <t>-32,84; -2,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 2,3</t>
+          <t>-49,9; -28,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 3,08</t>
+          <t>-21,14; 3,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,27; -7,89</t>
+          <t>-30,66; -8,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,56; -27,49</t>
+          <t>-46,24; -30,45</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-2,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,53</t>
+          <t>-9,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>-6,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 16,86</t>
+          <t>3,03; 17,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 6,3</t>
+          <t>-7,03; 6,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 4,1</t>
+          <t>-7,42; 3,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 8,85</t>
+          <t>-5,78; 8,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 0,9</t>
+          <t>-13,2; 0,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,1; -3,92</t>
+          <t>-15,22; -3,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 10,28</t>
+          <t>0,16; 10,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 1,73</t>
+          <t>-8,4; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -1,57</t>
+          <t>-10,34; -2,65</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-5,69%</t>
+          <t>-9,76%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,27%</t>
+          <t>-31,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-22,2%</t>
+          <t>-23,98%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11,42; 100,47</t>
+          <t>11,77; 97,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 37,75</t>
+          <t>-29,48; 38,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 24,31</t>
+          <t>-30,44; 24,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 32,53</t>
+          <t>-17,03; 30,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 3,13</t>
+          <t>-38,13; 1,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,56; -14,64</t>
+          <t>-43,46; -13,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,1; 44,15</t>
+          <t>0,51; 45,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 6,97</t>
+          <t>-29,03; 5,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,88; -6,87</t>
+          <t>-35,89; -11,31</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-10,08</t>
+          <t>-4,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,25</t>
+          <t>-2,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 10,58</t>
+          <t>-3,36; 10,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 13,59</t>
+          <t>-1,07; 13,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 5,7</t>
+          <t>-5,18; 5,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 6,03</t>
+          <t>-6,92; 6,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 7,88</t>
+          <t>-4,93; 7,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,37; -3,01</t>
+          <t>-10,54; 0,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 6,25</t>
+          <t>-3,17; 6,22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 8,61</t>
+          <t>-0,89; 9,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -0,65</t>
+          <t>-6,04; 1,37</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-48,8%</t>
+          <t>-23,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,25%</t>
+          <t>-13,78%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 118,54</t>
+          <t>-22,69; 108,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 151,86</t>
+          <t>-8,32; 145,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 65,55</t>
+          <t>-31,67; 59,14</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 36,48</t>
+          <t>-28,59; 36,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 46,07</t>
+          <t>-20,44; 43,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-82,65; -15,82</t>
+          <t>-42,91; 0,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 44,71</t>
+          <t>-17,35; 42,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 57,12</t>
+          <t>-4,89; 63,37</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,47; -4,41</t>
+          <t>-30,5; 10,17</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 7,84</t>
+          <t>-3,77; 8,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 10,29</t>
+          <t>-0,99; 10,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,48</t>
+          <t>-3,3; 6,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 5,77</t>
+          <t>-2,99; 5,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,17</t>
+          <t>0,77; 12,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,68</t>
+          <t>-2,26; 5,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,09</t>
+          <t>-2,04; 5,0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 10,59</t>
+          <t>1,81; 10,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,95</t>
+          <t>-1,09; 5,31</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 299,97</t>
+          <t>-50,11; 274,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 416,28</t>
+          <t>-21,95; 349,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,38; 264,99</t>
+          <t>-33,51; 288,73</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 219,53</t>
+          <t>-40,49; 189,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,91; 388,35</t>
+          <t>7,79; 404,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 182,97</t>
+          <t>-25,09; 179,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 144,03</t>
+          <t>-26,98; 143,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,63; 282,9</t>
+          <t>19,36; 280,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 141,75</t>
+          <t>-12,03; 170,46</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-14,05</t>
+          <t>-12,87</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-14,62</t>
+          <t>-13,74</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-14,34</t>
+          <t>-13,32</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,43</t>
+          <t>-4,62; 0,66</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -1,84</t>
+          <t>-7,29; -1,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -11,35</t>
+          <t>-15,4; -10,22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -0,57</t>
+          <t>-5,67; -0,78</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -3,24</t>
+          <t>-8,22; -3,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -11,76</t>
+          <t>-15,78; -11,66</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,98</t>
+          <t>-4,29; -0,76</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -3,27</t>
+          <t>-7,09; -3,47</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -12,24</t>
+          <t>-15,0; -11,61</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-43,91%</t>
+          <t>-40,24%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-45,59%</t>
+          <t>-42,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-44,78%</t>
+          <t>-41,6%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 1,46</t>
+          <t>-14,0; 2,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -5,48</t>
+          <t>-21,71; -5,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-57,45; -36,86</t>
+          <t>-45,86; -33,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -1,89</t>
+          <t>-17,05; -2,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -10,59</t>
+          <t>-24,94; -10,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-55,08; -37,47</t>
+          <t>-47,28; -38,05</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -3,14</t>
+          <t>-12,87; -2,34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -10,41</t>
+          <t>-21,54; -11,17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,4; -39,13</t>
+          <t>-45,33; -37,14</t>
         </is>
       </c>
     </row>
